--- a/mosip_master/xlsx/loc_holiday.xlsx
+++ b/mosip_master/xlsx/loc_holiday.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2000001</v>
+        <v>3000001</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2000001</v>
+        <v>3000002</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2000001</v>
+        <v>3000003</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2000002</v>
+        <v>3000004</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -612,7 +612,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2000002</v>
+        <v>3000005</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -647,7 +647,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2000002</v>
+        <v>3000006</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -682,7 +682,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2000003</v>
+        <v>3000007</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2000003</v>
+        <v>3000008</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2000003</v>
+        <v>3000009</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2000004</v>
+        <v>3000010</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2000004</v>
+        <v>3000011</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2000004</v>
+        <v>3000012</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2000005</v>
+        <v>3000013</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2000005</v>
+        <v>3000014</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -962,7 +962,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2000005</v>
+        <v>3000015</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2000006</v>
+        <v>3000016</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2000006</v>
+        <v>3000017</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2000006</v>
+        <v>3000018</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2000007</v>
+        <v>3000019</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2000007</v>
+        <v>3000020</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2000007</v>
+        <v>3000021</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2000008</v>
+        <v>3000022</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2000008</v>
+        <v>3000023</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2000008</v>
+        <v>3000024</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2000009</v>
+        <v>3000025</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2000009</v>
+        <v>3000026</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2000009</v>
+        <v>3000027</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2000010</v>
+        <v>3000028</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2000010</v>
+        <v>3000029</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2000010</v>
+        <v>3000030</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2000011</v>
+        <v>3000031</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2000011</v>
+        <v>3000032</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2000011</v>
+        <v>3000033</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2000012</v>
+        <v>3000034</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2000012</v>
+        <v>3000035</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2000012</v>
+        <v>3000036</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2000013</v>
+        <v>3000037</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2000013</v>
+        <v>3000038</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>2000013</v>
+        <v>3000039</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>2000014</v>
+        <v>3000040</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>2000014</v>
+        <v>3000041</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2000014</v>
+        <v>3000042</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>2000015</v>
+        <v>3000043</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>2000015</v>
+        <v>3000044</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>2000015</v>
+        <v>3000045</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2000016</v>
+        <v>3000046</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>2000016</v>
+        <v>3000047</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>2000016</v>
+        <v>3000048</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>2000017</v>
+        <v>3000049</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -2187,7 +2187,7 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>2000017</v>
+        <v>3000050</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>2000017</v>
+        <v>3000051</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>2000018</v>
+        <v>3000052</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -2292,7 +2292,7 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2000018</v>
+        <v>3000053</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2000018</v>
+        <v>3000054</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>2000019</v>
+        <v>3000055</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>2000019</v>
+        <v>3000056</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2000019</v>
+        <v>3000057</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>2000020</v>
+        <v>3000058</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>2000020</v>
+        <v>3000059</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>2000020</v>
+        <v>3000060</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>2000021</v>
+        <v>3000061</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -2607,7 +2607,7 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>2000021</v>
+        <v>3000062</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -2642,7 +2642,7 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>2000021</v>
+        <v>3000063</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>2000022</v>
+        <v>3000064</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>2000022</v>
+        <v>3000065</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>2000022</v>
+        <v>3000066</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>2000023</v>
+        <v>3000067</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>2000023</v>
+        <v>3000068</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>2000023</v>
+        <v>3000069</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>2000024</v>
+        <v>3000070</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>2000024</v>
+        <v>3000071</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>2000024</v>
+        <v>3000072</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>2000025</v>
+        <v>3000073</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>2000025</v>
+        <v>3000074</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>2000025</v>
+        <v>3000075</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -3097,7 +3097,7 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>2000026</v>
+        <v>3000076</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>2000026</v>
+        <v>3000077</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>2000026</v>
+        <v>3000078</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -3202,7 +3202,7 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>2000027</v>
+        <v>3000079</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>2000027</v>
+        <v>3000080</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -3272,7 +3272,7 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>2000027</v>
+        <v>3000081</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>2000028</v>
+        <v>3000082</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>2000028</v>
+        <v>3000083</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>2000028</v>
+        <v>3000084</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -3412,7 +3412,7 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>2000029</v>
+        <v>3000085</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -3447,7 +3447,7 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>2000029</v>
+        <v>3000086</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -3482,7 +3482,7 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>2000029</v>
+        <v>3000087</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>2000030</v>
+        <v>3000088</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>2000030</v>
+        <v>3000089</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -3587,7 +3587,7 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>2000030</v>
+        <v>3000090</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -3622,7 +3622,7 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>2000031</v>
+        <v>3000091</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -3657,7 +3657,7 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>2000031</v>
+        <v>3000092</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -3692,7 +3692,7 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>2000031</v>
+        <v>3000093</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>2000032</v>
+        <v>3000094</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -3762,7 +3762,7 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>2000032</v>
+        <v>3000095</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -3797,7 +3797,7 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>2000032</v>
+        <v>3000096</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -3832,7 +3832,7 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>2000033</v>
+        <v>3000097</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>2000033</v>
+        <v>3000098</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>2000033</v>
+        <v>3000099</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -3937,7 +3937,7 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>2000034</v>
+        <v>3000100</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -3972,7 +3972,7 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>2000034</v>
+        <v>3000101</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>2000034</v>
+        <v>3000102</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -4042,7 +4042,7 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>2000035</v>
+        <v>3000103</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -4077,7 +4077,7 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>2000035</v>
+        <v>3000104</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -4112,7 +4112,7 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>2000035</v>
+        <v>3000105</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -4147,7 +4147,7 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>2000036</v>
+        <v>3000106</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -4182,7 +4182,7 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>2000036</v>
+        <v>3000107</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -4217,7 +4217,7 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>2000036</v>
+        <v>3000108</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -4252,7 +4252,7 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>2000037</v>
+        <v>3000109</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -4287,7 +4287,7 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>2000037</v>
+        <v>3000110</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -4322,7 +4322,7 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>2000037</v>
+        <v>3000111</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -4357,7 +4357,7 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>2000038</v>
+        <v>3000112</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>2000038</v>
+        <v>3000113</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -4427,7 +4427,7 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>2000038</v>
+        <v>3000114</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -4462,7 +4462,7 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>2000039</v>
+        <v>3000115</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -4497,7 +4497,7 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>2000039</v>
+        <v>3000116</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -4532,7 +4532,7 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>2000039</v>
+        <v>3000117</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>2000040</v>
+        <v>3000118</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>2000040</v>
+        <v>3000119</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -4637,7 +4637,7 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>2000040</v>
+        <v>3000120</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -4672,7 +4672,7 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>2000041</v>
+        <v>3000121</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -4707,7 +4707,7 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>2000041</v>
+        <v>3000122</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -4742,7 +4742,7 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>2000041</v>
+        <v>3000123</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -4777,7 +4777,7 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>2000042</v>
+        <v>3000124</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -4812,7 +4812,7 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>2000042</v>
+        <v>3000125</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -4847,7 +4847,7 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>2000042</v>
+        <v>3000126</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -4882,7 +4882,7 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>2000043</v>
+        <v>3000127</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>2000043</v>
+        <v>3000128</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>2000043</v>
+        <v>3000129</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -4987,7 +4987,7 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>2000044</v>
+        <v>3000130</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>2000044</v>
+        <v>3000131</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -5057,7 +5057,7 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>2000044</v>
+        <v>3000132</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -5092,7 +5092,7 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>2000045</v>
+        <v>3000133</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -5127,7 +5127,7 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>2000045</v>
+        <v>3000134</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -5162,7 +5162,7 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>2000045</v>
+        <v>3000135</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -5197,7 +5197,7 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>2000046</v>
+        <v>3000136</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -5232,7 +5232,7 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>2000046</v>
+        <v>3000137</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>2000046</v>
+        <v>3000138</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>2000047</v>
+        <v>3000139</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>2000047</v>
+        <v>3000140</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -5372,7 +5372,7 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>2000047</v>
+        <v>3000141</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -5407,7 +5407,7 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>2000048</v>
+        <v>3000142</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -5442,7 +5442,7 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>2000048</v>
+        <v>3000143</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -5477,7 +5477,7 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>2000048</v>
+        <v>3000144</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -5512,7 +5512,7 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>2000049</v>
+        <v>3000145</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -5547,7 +5547,7 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>2000049</v>
+        <v>3000146</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -5582,7 +5582,7 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>2000049</v>
+        <v>3000147</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -5617,7 +5617,7 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>2000050</v>
+        <v>3000148</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -5652,7 +5652,7 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>2000050</v>
+        <v>3000149</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -5687,7 +5687,7 @@
         </is>
       </c>
       <c r="B151" t="n">
-        <v>2000050</v>
+        <v>3000150</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -5722,7 +5722,7 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>2000051</v>
+        <v>3000151</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -5757,7 +5757,7 @@
         </is>
       </c>
       <c r="B153" t="n">
-        <v>2000051</v>
+        <v>3000152</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -5792,7 +5792,7 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>2000051</v>
+        <v>3000153</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>

--- a/mosip_master/xlsx/loc_holiday.xlsx
+++ b/mosip_master/xlsx/loc_holiday.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G154"/>
+  <dimension ref="A1:G151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>May Day</t>
+          <t>May Day / Vesak Full Moon Poya Day</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>මැයි දිනය</t>
+          <t>මැයි දිනය / වෙසක් පුර පසළොස්වක පෝය</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>தொழிலாளர் தினம்</t>
+          <t>தொழிலாளர் தினம் / வேசாக் முழுநிலவு போய தினம்</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1741,17 +1741,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Vesak Full Moon Poya Day</t>
+          <t>Day following Vesak Full Moon Poya Day</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Full Moon Poya Day</t>
+          <t>Public Holiday</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -1776,17 +1776,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>වෙසක් පුර පසළොස්වක පෝය</t>
+          <t>වෙසක් පෝයට පසු දිනය</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>පුර පසළොස්වක පෝය</t>
+          <t>රජයේ නිවාඩු දිනය</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -1811,17 +1811,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>வேசாக் முழுநிலவு போய தினம்</t>
+          <t>வேசாக் போய தினத்திற்கு அடுத்த நாள்</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>முழுநிலவு போய தினம்</t>
+          <t>அரசு விடுமுறை நாள்</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Day following Vesak Full Moon Poya Day</t>
+          <t>Eid-Ul-Allha (Hadji)</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>වෙසක් පෝයට පසු දිනය</t>
+          <t>ඊද්-උල්-අල්හා (හජ්)</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>வேசாக் போய தினத்திற்கு அடுத்த நாள்</t>
+          <t>ஈத்-உல்-அழ்ஹா (ஹஜ்)</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1951,17 +1951,17 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Eid-Ul-Allha (Hadji)</t>
+          <t>Adhi Poson Full Moon Poya Day</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Public Holiday</t>
+          <t>Full Moon Poya Day</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -1986,17 +1986,17 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>ඊද්-උල්-අල්හා (හජ්)</t>
+          <t>අධි පොසොන් පුර පසළොස්වක පෝය</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>රජයේ නිවාඩු දිනය</t>
+          <t>පුර පසළොස්වක පෝය</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2021,17 +2021,17 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>ஈத்-உல்-அழ்ஹா (ஹஜ்)</t>
+          <t>அதி போசொன் முழுநிலவு போய தினம்</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>அரசு விடுமுறை நாள்</t>
+          <t>முழுநிலவு போய தினம்</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2056,12 +2056,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Adhi Poson Full Moon Poya Day</t>
+          <t>Poson Full Moon Poya Day</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2091,12 +2091,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>අධි පොසොන් පුර පසළොස්වක පෝය</t>
+          <t>පොසොන් පුර පසළොස්වක පෝය</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2126,12 +2126,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>அதி போசொன் முழுநிலவு போய தினம்</t>
+          <t>போசொன் முழுநிலவு போய தினம்</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2161,12 +2161,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Poson Full Moon Poya Day</t>
+          <t>Esala Full Moon Poya Day</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2196,12 +2196,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>පොසොන් පුර පසළොස්වක පෝය</t>
+          <t>ඇසළ පුර පසළොස්වක පෝය</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2231,12 +2231,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>போசொன் முழுநிலவு போய தினம்</t>
+          <t>எசல முழுநிலவு போய தினம்</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2266,17 +2266,17 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Esala Full Moon Poya Day</t>
+          <t>Milad-Un-Nabi</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Full Moon Poya Day</t>
+          <t>Public Holiday</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>ඇසළ පුර පසළොස්වක පෝය</t>
+          <t>මිලාද්-උන්-නබි</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>පුර පසළොස්වක පෝය</t>
+          <t>රජයේ නිවාඩු දිනය</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2336,17 +2336,17 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>எசல முழுநிலவு போய தினம்</t>
+          <t>மிலாதுன் நபி</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>முழுநிலவு போய தினம்</t>
+          <t>அரசு விடுமுறை நாள்</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2371,17 +2371,17 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Milad-Un-Nabi</t>
+          <t>Nikini Full Moon Poya Day</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Public Holiday</t>
+          <t>Full Moon Poya Day</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -2406,17 +2406,17 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>මිලාද්-උන්-නබි</t>
+          <t>නිකිණි පුර පසළොස්වක පෝය</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>රජයේ නිවාඩු දිනය</t>
+          <t>පුර පසළොස්වක පෝය</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2441,17 +2441,17 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>மிலாதுன் நபி</t>
+          <t>நிகிணி முழுநிலவு போய தினம்</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>அரசு விடுமுறை நாள்</t>
+          <t>முழுநிலவு போய தினம்</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2476,12 +2476,12 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Nikini Full Moon Poya Day</t>
+          <t>Binara Full Moon Poya Day</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2511,12 +2511,12 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>නිකිණි පුර පසළොස්වක පෝය</t>
+          <t>බිනර පුර පසළොස්වක පෝය</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2546,12 +2546,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>நிகிணி முழுநிலவு போய தினம்</t>
+          <t>பினர முழுநிலவு போய தினம்</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Binara Full Moon Poya Day</t>
+          <t>Vap Full Moon Poya Day</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>බිනර පුර පසළොස්වක පෝය</t>
+          <t>වප් පුර පසළොස්වක පෝය</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2651,12 +2651,12 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>பினர முழுநிலவு போய தினம்</t>
+          <t>வப் முழுநிலவு போய தினம்</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2686,17 +2686,17 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-11-08</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Vap Full Moon Poya Day</t>
+          <t>Deepawali Festival Day</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Full Moon Poya Day</t>
+          <t>Public Holiday</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -2721,17 +2721,17 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-11-08</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>වප් පුර පසළොස්වක පෝය</t>
+          <t>දීපාවලි උත්සව දිනය</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>පුර පසළොස්වක පෝය</t>
+          <t>රජයේ නිවාඩු දිනය</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -2756,17 +2756,17 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-11-08</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>வப் முழுநிலவு போய தினம்</t>
+          <t>தீபாவளி திருநாள்</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>முழுநிலவு போய தினம்</t>
+          <t>அரசு விடுமுறை நாள்</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -2791,17 +2791,17 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Deepawali Festival Day</t>
+          <t>Ill Full Moon Poya Day</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Public Holiday</t>
+          <t>Full Moon Poya Day</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -2826,17 +2826,17 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>දීපාවලි උත්සව දිනය</t>
+          <t>ඉල් පුර පසළොස්වක පෝය</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>රජයේ නිවාඩු දිනය</t>
+          <t>පුර පසළොස්වක පෝය</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -2861,17 +2861,17 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>தீபாவளி திருநாள்</t>
+          <t>இல் முழுநிலவு போய தினம்</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>அரசு விடுமுறை நாள்</t>
+          <t>முழுநிலவு போய தினம்</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -2896,12 +2896,12 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Ill Full Moon Poya Day</t>
+          <t>Unduvap Full Moon Poya Day</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>ඉල් පුර පසළොස්වක පෝය</t>
+          <t>උඳුවප් පුර පසළොස්වක පෝය</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2966,12 +2966,12 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>இல் முழுநிலவு போய தினம்</t>
+          <t>உந்துவப் முழுநிலவு போய தினம்</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -3001,17 +3001,17 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Unduvap Full Moon Poya Day</t>
+          <t>Christmas Day</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Full Moon Poya Day</t>
+          <t>Public Holiday</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -3036,17 +3036,17 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>උඳුවප් පුර පසළොස්වක පෝය</t>
+          <t>නත්තල් දිනය</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>පුර පසළොස්වක පෝය</t>
+          <t>රජයේ නිවාඩු දිනය</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -3071,17 +3071,17 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>உந்துவப் முழுநிலவு போய தினம்</t>
+          <t>கிறிஸ்துமஸ் தினம்</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>முழுநிலவு போய தினம்</t>
+          <t>அரசு விடுமுறை நாள்</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -3106,12 +3106,12 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2027-01-15</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Christmas Day</t>
+          <t>Tamil Thai Pongal Day</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2027-01-15</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>නත්තල් දිනය</t>
+          <t>දෙමළ තෛපොංගල් දිනය</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2027-01-15</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>கிறிஸ்துமஸ் தினம்</t>
+          <t>தமிழ் தைப்பொங்கல் தினம்</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3211,17 +3211,17 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>2027-01-22</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Tamil Thai Pongal Day</t>
+          <t>Duruthu Full Moon Poya Day</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Public Holiday</t>
+          <t>Full Moon Poya Day</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -3246,17 +3246,17 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>2027-01-22</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>දෙමළ තෛපොංගල් දිනය</t>
+          <t>දුරුතු පුර පසළොස්වක පෝය</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>රජයේ නිවාඩු දිනය</t>
+          <t>පුර පසළොස්වක පෝය</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -3281,17 +3281,17 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>2027-01-22</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>தமிழ் தைப்பொங்கல் தினம்</t>
+          <t>துருது முழுநிலவு போய தினம்</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>அரசு விடுமுறை நாள்</t>
+          <t>முழுநிலவு போய தினம்</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -3316,17 +3316,17 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2027-01-22</t>
+          <t>2027-02-04</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Duruthu Full Moon Poya Day</t>
+          <t>National Day</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Full Moon Poya Day</t>
+          <t>Public Holiday</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -3351,17 +3351,17 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2027-01-22</t>
+          <t>2027-02-04</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>දුරුතු පුර පසළොස්වක පෝය</t>
+          <t>ජාතික නිදහස් දිනය</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>පුර පසළොස්වක පෝය</t>
+          <t>රජයේ නිවාඩු දිනය</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -3386,17 +3386,17 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2027-01-22</t>
+          <t>2027-02-04</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>துருது முழுநிலவு போய தினம்</t>
+          <t>தேசிய சுதந்திர தினம்</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>முழுநிலவு போய தினம்</t>
+          <t>அரசு விடுமுறை நாள்</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -3421,17 +3421,17 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2027-02-04</t>
+          <t>2027-02-20</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>National Day</t>
+          <t>Navam Full Moon Poya Day</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Public Holiday</t>
+          <t>Full Moon Poya Day</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3456,17 +3456,17 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2027-02-04</t>
+          <t>2027-02-20</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>ජාතික නිදහස් දිනය</t>
+          <t>නවම් පුර පසළොස්වක පෝය</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>රජයේ නිවාඩු දිනය</t>
+          <t>පුර පසළොස්වක පෝය</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -3491,17 +3491,17 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2027-02-04</t>
+          <t>2027-02-20</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>தேசிய சுதந்திர தினம்</t>
+          <t>நவம் முழுநிலவு போய தினம்</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>அரசு விடுமுறை நாள்</t>
+          <t>முழுநிலவு போய தினம்</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -3526,17 +3526,17 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2027-02-20</t>
+          <t>2027-03-06</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Navam Full Moon Poya Day</t>
+          <t>Mahasivarathri Day</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Full Moon Poya Day</t>
+          <t>Public Holiday</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -3561,17 +3561,17 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2027-02-20</t>
+          <t>2027-03-06</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>නවම් පුර පසළොස්වක පෝය</t>
+          <t>මහා ශිවරාත්‍රී දිනය</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>පුර පසළොස්වක පෝය</t>
+          <t>රජයේ නිවාඩු දිනය</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -3596,17 +3596,17 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2027-02-20</t>
+          <t>2027-03-06</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>நவம் முழுநிலவு போய தினம்</t>
+          <t>மகா சிவராத்திரி தினம்</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>முழுநிலவு போய தினம்</t>
+          <t>அரசு விடுமுறை நாள்</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -3631,12 +3631,12 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2027-03-06</t>
+          <t>2027-03-10</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Mahasivarathri Day</t>
+          <t>Id Ul-Fitr</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3666,12 +3666,12 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2027-03-06</t>
+          <t>2027-03-10</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>මහා ශිවරාත්‍රී දිනය</t>
+          <t>ඊද්-උල්-ෆීතර් (රාමසාන්)</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2027-03-06</t>
+          <t>2027-03-10</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>மகா சிவராத்திரி தினம்</t>
+          <t>ஈத்-உல்-ஃபித்ர் (ரமலான்)</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3736,17 +3736,17 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2027-03-10</t>
+          <t>2027-03-21</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Id Ul-Fitr</t>
+          <t>Madin Full Moon Poya Day</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Public Holiday</t>
+          <t>Full Moon Poya Day</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -3771,17 +3771,17 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2027-03-10</t>
+          <t>2027-03-21</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>ඊද්-උල්-ෆීතර් (රාමසාන්)</t>
+          <t>මැදින් පුර පසළොස්වක පෝය</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>රජයේ නිවාඩු දිනය</t>
+          <t>පුර පසළොස්වක පෝය</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -3806,17 +3806,17 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2027-03-10</t>
+          <t>2027-03-21</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>ஈத்-உல்-ஃபித்ர் (ரமலான்)</t>
+          <t>மதின் முழுநிலவு போய தினம்</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>அரசு விடுமுறை நாள்</t>
+          <t>முழுநிலவு போய தினம்</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -3841,17 +3841,17 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2027-03-21</t>
+          <t>2027-03-26</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Madin Full Moon Poya Day</t>
+          <t>Good Friday</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Full Moon Poya Day</t>
+          <t>Public Holiday</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -3876,17 +3876,17 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2027-03-21</t>
+          <t>2027-03-26</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>මැදින් පුර පසළොස්වක පෝය</t>
+          <t>මහ සිකුරාදා</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>පුර පසළොස්වක පෝය</t>
+          <t>රජයේ නිවාඩු දිනය</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -3911,17 +3911,17 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2027-03-21</t>
+          <t>2027-03-26</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>மதின் முழுநிலவு போய தினம்</t>
+          <t>புனித வெள்ளி</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>முழுநிலவு போய தினம்</t>
+          <t>அரசு விடுமுறை நாள்</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -3946,12 +3946,12 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2027-03-26</t>
+          <t>2027-04-13</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Good Friday</t>
+          <t>Day prior to Sinhala &amp; Tamil New Year Day</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2027-03-26</t>
+          <t>2027-04-13</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>මහ සිකුරාදා</t>
+          <t>සිංහල සහ දෙමළ අලුත් අවුරුදු උදාව</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -4016,12 +4016,12 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2027-03-26</t>
+          <t>2027-04-13</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>புனித வெள்ளி</t>
+          <t>சிங்கள தமிழ் புத்தாண்டு தலையான நாள்</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4051,12 +4051,12 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2027-04-13</t>
+          <t>2027-04-14</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Day prior to Sinhala &amp; Tamil New Year Day</t>
+          <t>Sinhala &amp; Tamil New Year Day</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2027-04-13</t>
+          <t>2027-04-14</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>සිංහල සහ දෙමළ අලුත් අවුරුදු උදාව</t>
+          <t>සිංහල සහ දෙමළ අලුත් අවුරුදු දිනය</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2027-04-13</t>
+          <t>2027-04-14</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>சிங்கள தமிழ் புத்தாண்டு தலையான நாள்</t>
+          <t>சிங்கள தமிழ் புத்தாண்டு தினம்</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4156,17 +4156,17 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2027-04-14</t>
+          <t>2027-04-20</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Sinhala &amp; Tamil New Year Day</t>
+          <t>Bak Full Moon Poya Day</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Public Holiday</t>
+          <t>Full Moon Poya Day</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -4191,17 +4191,17 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2027-04-14</t>
+          <t>2027-04-20</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>සිංහල සහ දෙමළ අලුත් අවුරුදු දිනය</t>
+          <t>බක් පුර පසළොස්වක පෝය</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>රජයේ නිවාඩු දිනය</t>
+          <t>පුර පසළොස්වක පෝය</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -4226,17 +4226,17 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2027-04-14</t>
+          <t>2027-04-20</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>சிங்கள தமிழ் புத்தாண்டு தினம்</t>
+          <t>பக் முழுநிலவு போய தினம்</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>அரசு விடுமுறை நாள்</t>
+          <t>முழுநிலவு போய தினம்</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -4261,17 +4261,17 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2027-04-20</t>
+          <t>2027-05-01</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Bak Full Moon Poya Day</t>
+          <t>May Day</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Full Moon Poya Day</t>
+          <t>Public Holiday</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -4296,17 +4296,17 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2027-04-20</t>
+          <t>2027-05-01</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>බක් පුර පසළොස්වක පෝය</t>
+          <t>මැයි දිනය</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>පුර පසළොස්වක පෝය</t>
+          <t>රජයේ නිවාඩු දිනය</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -4331,17 +4331,17 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2027-04-20</t>
+          <t>2027-05-01</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>பக் முழுநிலவு போய தினம்</t>
+          <t>தொழிலாளர் தினம்</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>முழுநிலவு போய தினம்</t>
+          <t>அரசு விடுமுறை நாள்</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -4366,12 +4366,12 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2027-05-01</t>
+          <t>2027-05-17</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>May Day</t>
+          <t>Id Ul-Alha</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2027-05-01</t>
+          <t>2027-05-17</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>මැයි දිනය</t>
+          <t>ඊද්-උල්-අල්හා (හජ්)</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4436,12 +4436,12 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2027-05-01</t>
+          <t>2027-05-17</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>தொழிலாளர் தினம்</t>
+          <t>ஈத்-உல்-அழ்ஹா (ஹஜ்)</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4471,17 +4471,17 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2027-05-17</t>
+          <t>2027-05-20</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Id Ul-Alha</t>
+          <t>Vesak Full Moon Poya Day</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Public Holiday</t>
+          <t>Full Moon Poya Day</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -4506,17 +4506,17 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2027-05-17</t>
+          <t>2027-05-20</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>ඊද්-උල්-අල්හා (හජ්)</t>
+          <t>වෙසක් පුර පසළොස්වක පෝය</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>රජයේ නිවාඩු දිනය</t>
+          <t>පුර පසළොස්වක පෝය</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -4541,17 +4541,17 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2027-05-17</t>
+          <t>2027-05-20</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>ஈத்-உல்-அழ்ஹா (ஹஜ்)</t>
+          <t>வேசாக் முழுநிலவு போய தினம்</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>அரசு விடுமுறை நாள்</t>
+          <t>முழுநிலவு போய தினம்</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -4576,17 +4576,17 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2027-05-20</t>
+          <t>2027-05-21</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Vesak Full Moon Poya Day</t>
+          <t>Day following Vesak Full Moon Poya Day</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Full Moon Poya Day</t>
+          <t>Public Holiday</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -4611,17 +4611,17 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2027-05-20</t>
+          <t>2027-05-21</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>වෙසක් පුර පසළොස්වක පෝය</t>
+          <t>වෙසක් පෝයට පසු දිනය</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>පුර පසළොස්වක පෝය</t>
+          <t>රජයේ නිවාඩු දිනය</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -4646,17 +4646,17 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2027-05-20</t>
+          <t>2027-05-21</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>வேசாக் முழுநிலவு போய தினம்</t>
+          <t>வேசாக் போய தினத்திற்கு அடுத்த நாள்</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>முழுநிலவு போய தினம்</t>
+          <t>அரசு விடுமுறை நாள்</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -4681,17 +4681,17 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2027-05-21</t>
+          <t>2027-06-18</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Day following Vesak Full Moon Poya Day</t>
+          <t>Poson Full Moon Poya Day</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Public Holiday</t>
+          <t>Full Moon Poya Day</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -4716,17 +4716,17 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2027-05-21</t>
+          <t>2027-06-18</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>වෙසක් පෝයට පසු දිනය</t>
+          <t>පොසොන් පුර පසළොස්වක පෝය</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>රජයේ නිවාඩු දිනය</t>
+          <t>පුර පසළොස්වක පෝය</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -4751,17 +4751,17 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2027-05-21</t>
+          <t>2027-06-18</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>வேசாக் போய தினத்திற்கு அடுத்த நாள்</t>
+          <t>போசொன் முழுநிலவு போய தினம்</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>அரசு விடுமுறை நாள்</t>
+          <t>முழுநிலவு போய தினம்</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -4786,12 +4786,12 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2027-06-18</t>
+          <t>2027-07-18</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Poson Full Moon Poya Day</t>
+          <t>Esala Full Moon Poya Day</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4821,12 +4821,12 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2027-06-18</t>
+          <t>2027-07-18</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>පොසොන් පුර පසළොස්වක පෝය</t>
+          <t>ඇසළ පුර පසළොස්වක පෝය</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4856,12 +4856,12 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2027-06-18</t>
+          <t>2027-07-18</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>போசொன் முழுநிலவு போய தினம்</t>
+          <t>எசல முழுநிலவு போய தினம்</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4891,17 +4891,17 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2027-07-18</t>
+          <t>2027-08-15</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Esala Full Moon Poya Day</t>
+          <t>Milad un-Nabi</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Full Moon Poya Day</t>
+          <t>Public Holiday</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -4926,17 +4926,17 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2027-07-18</t>
+          <t>2027-08-15</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>ඇසළ පුර පසළොස්වක පෝය</t>
+          <t>මිලාද්-උන්-නබි</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>පුර පසළොස්වක පෝය</t>
+          <t>රජයේ නිවාඩු දිනය</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -4961,17 +4961,17 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2027-07-18</t>
+          <t>2027-08-15</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>எசல முழுநிலவு போய தினம்</t>
+          <t>மிலாதுன் நபி</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>முழுநிலவு போய தினம்</t>
+          <t>அரசு விடுமுறை நாள்</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -4996,17 +4996,17 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2027-08-15</t>
+          <t>2027-08-16</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Milad un-Nabi</t>
+          <t>Nikini Full Moon Poya Day</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Public Holiday</t>
+          <t>Full Moon Poya Day</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -5031,17 +5031,17 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2027-08-15</t>
+          <t>2027-08-16</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>මිලාද්-උන්-නබි</t>
+          <t>නිකිණි පුර පසළොස්වක පෝය</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>රජයේ නිවාඩු දිනය</t>
+          <t>පුර පසළොස්වක පෝය</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -5066,17 +5066,17 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2027-08-15</t>
+          <t>2027-08-16</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>மிலாதுன் நபி</t>
+          <t>நிகிணி முழுநிலவு போய தினம்</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>அரசு விடுமுறை நாள்</t>
+          <t>முழுநிலவு போய தினம்</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -5101,12 +5101,12 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2027-08-16</t>
+          <t>2027-09-15</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Nikini Full Moon Poya Day</t>
+          <t>Binara Full Moon Poya Day</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2027-08-16</t>
+          <t>2027-09-15</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>නිකිණි පුර පසළොස්වක පෝය</t>
+          <t>බිනර පුර පසළොස්වක පෝය</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2027-08-16</t>
+          <t>2027-09-15</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>நிகிணி முழுநிலவு போய தினம்</t>
+          <t>பினர முழுநிலவு போய தினம்</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5206,12 +5206,12 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2027-09-15</t>
+          <t>2027-10-15</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Binara Full Moon Poya Day</t>
+          <t>Vap Full Moon Poya Day</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5241,12 +5241,12 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2027-09-15</t>
+          <t>2027-10-15</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>බිනර පුර පසළොස්වක පෝය</t>
+          <t>වප් පුර පසළොස්වක පෝය</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5276,12 +5276,12 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2027-09-15</t>
+          <t>2027-10-15</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>பினர முழுநிலவு போய தினம்</t>
+          <t>வப் முழுநிலவு போய தினம்</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5311,17 +5311,17 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2027-10-15</t>
+          <t>2027-10-28</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Vap Full Moon Poya Day</t>
+          <t>Deepavali</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Full Moon Poya Day</t>
+          <t>Public Holiday</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -5346,17 +5346,17 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2027-10-15</t>
+          <t>2027-10-28</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>වප් පුර පසළොස්වක පෝය</t>
+          <t>දීපාවලි උත්සව දිනය</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>පුර පසළොස්වක පෝය</t>
+          <t>රජයේ නිවාඩු දිනය</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -5381,17 +5381,17 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2027-10-15</t>
+          <t>2027-10-28</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>வப் முழுநிலவு போய தினம்</t>
+          <t>தீபாவளி திருநாள்</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>முழுநிலவு போய தினம்</t>
+          <t>அரசு விடுமுறை நாள்</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -5416,17 +5416,17 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2027-10-28</t>
+          <t>2027-11-13</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Deepavali</t>
+          <t>Ill Full Moon Poya Day</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Public Holiday</t>
+          <t>Full Moon Poya Day</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -5451,17 +5451,17 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2027-10-28</t>
+          <t>2027-11-13</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>දීපාවලි උත්සව දිනය</t>
+          <t>ඉල් පුර පසළොස්වක පෝය</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>රජයේ නිවාඩු දිනය</t>
+          <t>පුර පසළොස්වක පෝය</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -5486,17 +5486,17 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2027-10-28</t>
+          <t>2027-11-13</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>தீபாவளி திருநாள்</t>
+          <t>இல் முழுநிலவு போய தினம்</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>அரசு விடுமுறை நாள்</t>
+          <t>முழுநிலவு போய தினம்</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -5521,12 +5521,12 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2027-11-13</t>
+          <t>2027-12-13</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Ill Full Moon Poya Day</t>
+          <t>Unduvap Full Moon Poya Day</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2027-11-13</t>
+          <t>2027-12-13</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>ඉල් පුර පසළොස්වක පෝය</t>
+          <t>උඳුවප් පුර පසළොස්වක පෝය</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2027-11-13</t>
+          <t>2027-12-13</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>இல் முழுநிலவு போய தினம்</t>
+          <t>உந்துவப் முழுநிலவு போய தினம்</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -5626,17 +5626,17 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2027-12-13</t>
+          <t>2027-12-25</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Unduvap Full Moon Poya Day</t>
+          <t>Christmas Day</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Full Moon Poya Day</t>
+          <t>Public Holiday</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -5661,17 +5661,17 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2027-12-13</t>
+          <t>2027-12-25</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>උඳුවප් පුර පසළොස්වක පෝය</t>
+          <t>නත්තල් දිනය</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>පුර පසළොස්වක පෝය</t>
+          <t>රජයේ නිවාඩු දිනය</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -5696,125 +5696,20 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2027-12-13</t>
+          <t>2027-12-25</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>உந்துவப் முழுநிலவு போய தினம்</t>
+          <t>கிறிஸ்துமஸ் தினம்</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>முழுநிலவு போய தினம்</t>
+          <t>அரசு விடுமுறை நாள்</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>eng</t>
-        </is>
-      </c>
-      <c r="B152" t="n">
-        <v>3000151</v>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>LKA</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>2027-12-25</t>
-        </is>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>Christmas Day</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>Public Holiday</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>sin</t>
-        </is>
-      </c>
-      <c r="B153" t="n">
-        <v>3000152</v>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>LKA</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>2027-12-25</t>
-        </is>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>නත්තල් දිනය</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>රජයේ නිවාඩු දිනය</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>tam</t>
-        </is>
-      </c>
-      <c r="B154" t="n">
-        <v>3000153</v>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>LKA</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>2027-12-25</t>
-        </is>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>கிறிஸ்துமஸ் தினம்</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>அரசு விடுமுறை நாள்</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
